--- a/JobIntel/sql/query_results/top_skills.xlsx
+++ b/JobIntel/sql/query_results/top_skills.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42a4dbeb8f84b5af/Desktop/AI-Powered-Job-Market-Intelligence-Platform/AI-Powered-Job-Market-Intelligence-Platform/JobIntel/sql/query_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DB47244-1C6C-4237-AB71-52095563A496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{1DB47244-1C6C-4237-AB71-52095563A496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBD0B499-4AE0-4397-BB71-65ED30C9C62B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0CDE1D4A-84C6-4EA6-A454-58D6B970CD43}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>communication</t>
   </si>
@@ -87,13 +87,19 @@
     <t>statistics</t>
   </si>
   <si>
-    <t>html</t>
-  </si>
-  <si>
     <t>machine learning</t>
   </si>
   <si>
     <t>linux</t>
+  </si>
+  <si>
+    <t>scrum</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>demand</t>
   </si>
 </sst>
 </file>
@@ -445,167 +451,175 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F883325-80DD-41F0-B6A8-4FA543F6B548}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>59998</v>
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>29355</v>
+        <v>59773</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>18107</v>
+        <v>29228</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>10229</v>
+        <v>18079</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>8801</v>
+        <v>9981</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>5969</v>
+        <v>8799</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>5183</v>
+        <v>5931</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>4648</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>3239</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>3161</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>2976</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>2918</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>2664</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>2457</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>2339</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>1961</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>1772</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19">
-        <v>1710</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>1701</v>
+      <c r="B21">
+        <v>1556</v>
       </c>
     </row>
   </sheetData>
